--- a/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCAC56E-4D2A-48F1-B23A-790F2A577318}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34808F3B-D7C4-4ED4-A616-9DA76F94B777}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,6 +13,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -317,6 +320,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -329,7 +333,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -694,7 +697,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -714,11 +717,9 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>3000</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -762,7 +763,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
@@ -773,7 +774,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
       <c r="B3" t="s">
         <v>20</v>
       </c>
@@ -782,7 +783,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" t="s">
         <v>22</v>
       </c>
@@ -791,7 +792,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B5" t="s">
@@ -802,7 +803,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -811,7 +812,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -820,7 +821,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -829,7 +830,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="9"/>
       <c r="B9" t="s">
         <v>33</v>
       </c>
@@ -838,7 +839,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
@@ -849,7 +850,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="10"/>
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -858,7 +859,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B12" t="s">
@@ -869,7 +870,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="10"/>
+      <c r="A13" s="11"/>
       <c r="B13" t="s">
         <v>43</v>
       </c>
@@ -878,7 +879,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="10"/>
+      <c r="A14" s="11"/>
       <c r="B14" t="s">
         <v>45</v>
       </c>
@@ -920,8 +921,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd739a91710fed73edeed3c312976475">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="829e6ebd84bdd7e43dc34d34aecb984e" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -945,6 +966,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1020,6 +1042,11 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fb9e4d32-074f-4c04-81ef-e811753dfd59" elementFormDefault="qualified">
@@ -1162,28 +1189,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522AEC49-A4CA-4308-847D-9BB5F1A751E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D518B4E-C20A-4FFC-BC13-992313191C2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1191,5 +1198,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D518B4E-C20A-4FFC-BC13-992313191C2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C22A88-BD58-4ADE-9D27-BFDC07A9CF90}"/>
 </file>
--- a/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27321"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34808F3B-D7C4-4ED4-A616-9DA76F94B777}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0951568A-30A6-4C89-BDC7-2AFB0687589C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,8 +31,53 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={C770F223-8A8B-42FA-9D91-BA1B0A4993EA}</author>
+    <author>tc={C0BF61DB-B43C-4CD2-A0BE-74248732DEF7}</author>
+    <author>tc={C4BB2CCB-5C6B-47ED-91E8-F60C68E277EF}</author>
+    <author>tc={DF6CEAC2-5C0E-4508-9A40-1233D6B29A76}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{C770F223-8A8B-42FA-9D91-BA1B0A4993EA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please select a category</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{C0BF61DB-B43C-4CD2-A0BE-74248732DEF7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the baseline in terms of number of beneficiaires</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{C4BB2CCB-5C6B-47ED-91E8-F60C68E277EF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the target in terms of number of beneficiaries target</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{DF6CEAC2-5C0E-4508-9A40-1233D6B29A76}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please provide any assumption or comments on how you estimate the number of beneficiaries</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>Project ID</t>
   </si>
@@ -64,6 +109,39 @@
     <t>Donors</t>
   </si>
   <si>
+    <t>Gender (% female)</t>
+  </si>
+  <si>
+    <t>VF or Non-VF</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>SEH Taxonomy</t>
+  </si>
+  <si>
+    <t>RISE Taxonomy</t>
+  </si>
+  <si>
+    <t>Flagship</t>
+  </si>
+  <si>
+    <t>Indirect Category</t>
+  </si>
+  <si>
+    <t>Indirect Taxonomy</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
+  </si>
+  <si>
     <t>Support to SDGs localization in Ukraine</t>
   </si>
   <si>
@@ -79,58 +157,145 @@
     <t>PIMS+</t>
   </si>
   <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Access to Energy</t>
+    <t>001000157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotion of Human Security </t>
   </si>
   <si>
     <t>Electricity Access</t>
   </si>
   <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Access to electricity (direct access to electricity, lighting, heating, cooling, etc)</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/press-releases/undp-and-japan-deliver-high-power-autotransformers-ukraine-ensure-unbroken-energy-supplies-over-half-million-people</t>
+  </si>
+  <si>
+    <t>No. of Beneficaries</t>
+  </si>
+  <si>
+    <t>-4 Autotransformers (2 installed, 2 upcoming)</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/press-releases/japan-undp-deliver-equipment-secure-power-supply-over-55-million-ukrainians</t>
+  </si>
+  <si>
+    <t>-Transporation Support for 7 Autotransformers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 gas turbine for power generation </t>
+  </si>
+  <si>
+    <t>00134106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winterization/Energy Sector Recovery </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2 gas turbine for power generation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 gas compressor </t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>-Transportation Support for 2 Autotransformers</t>
+  </si>
+  <si>
+    <t>-1 gas pistons power generation system</t>
+  </si>
+  <si>
+    <t>-25 bushings (750kV)</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>-15 bushings (330kV)</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>-1 Autotransformer (upcoming)</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
   </si>
   <si>
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
+    <t>Number of MW installed capacity</t>
   </si>
   <si>
     <t>Clean Cooking</t>
   </si>
   <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Access to agricultural energy services (irrigation with solar pumps, heating systems for processing food, etc. )</t>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
   </si>
   <si>
     <t>Health Services</t>
   </si>
   <si>
-    <t>Access to health services powered by solar PV and energy efficient systems such as hospitals</t>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
   </si>
   <si>
     <t>Water Services</t>
   </si>
   <si>
-    <t>Access to solar water pumps</t>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
   </si>
   <si>
     <t>Education Services</t>
   </si>
   <si>
-    <t>Access to education services trough clean energy systems</t>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -139,7 +304,10 @@
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t>Market Development</t>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Medium Enterprises</t>
@@ -154,13 +322,10 @@
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t>Individuals who participate in trainings for energy activities</t>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
   </si>
   <si>
     <t>Entrepreneurship Training</t>
@@ -169,19 +334,19 @@
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
   </si>
   <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
     <t>Campaign Participant</t>
   </si>
   <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
   </si>
   <si>
-    <t>Policy and Regulator Frameworks</t>
-  </si>
-  <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
-    <t>Policies and regulatory framework can have far-reaching impacts on the energy access situation in countries</t>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
   </si>
   <si>
     <t>Other</t>
@@ -194,12 +359,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -224,8 +398,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,44 +432,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FFFFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42FFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00E1DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BDB7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -298,45 +456,532 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -349,6 +994,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Stefano Pistolese" id="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" userId="S::stefano.pistolese@undp.org::a561415f-6f58-4f47-821a-08ad5d654fc1" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -636,31 +1287,54 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2023-11-14T00:24:52.08" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{C770F223-8A8B-42FA-9D91-BA1B0A4993EA}">
+    <text>Please select a category</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2023-11-14T00:24:31.19" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{C0BF61DB-B43C-4CD2-A0BE-74248732DEF7}">
+    <text>Please insert the baseline in terms of number of beneficiaires</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2023-11-14T00:23:33.06" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{C4BB2CCB-5C6B-47ED-91E8-F60C68E277EF}">
+    <text>Please insert the target in terms of number of beneficiaries target</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2023-11-14T00:25:34.71" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{DF6CEAC2-5C0E-4508-9A40-1233D6B29A76}">
+    <text>Please provide any assumption or comments on how you estimate the number of beneficiaries</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="20.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:23">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -675,67 +1349,677 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="45" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="K1" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>99918</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" s="33" t="s">
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
+        <v>22</v>
+      </c>
+      <c r="D2" s="33">
         <v>6817448</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
+      <c r="I2" s="39"/>
+      <c r="J2" s="41"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="16"/>
+      <c r="W2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" s="17">
         <v>4114</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3">
+      <c r="B3" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="34">
         <v>5480000</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="K3" s="7" t="s">
-        <v>12</v>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="22"/>
+      <c r="W3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="63">
+        <v>40000000</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="26"/>
+      <c r="W4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="61"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="64"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="37">
+        <v>1000000</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="52"/>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="16"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="61"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="64"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1500000</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="52"/>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="16"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="62"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0</v>
+      </c>
+      <c r="H7" s="38">
+        <v>1500000</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="K7" s="17">
+        <v>50</v>
+      </c>
+      <c r="L7" s="19"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="22"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="72" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="49">
+        <v>64600000</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="17">
+        <v>0</v>
+      </c>
+      <c r="H8" s="38">
+        <v>2500000</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="17">
+        <v>50</v>
+      </c>
+      <c r="L8" s="27"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="30"/>
+      <c r="W8" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="73"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="66">
+        <v>9600000</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="37">
+        <v>250000</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="26"/>
+      <c r="W9" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="73"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="37">
+        <v>500000</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="52"/>
+      <c r="K10">
+        <v>50</v>
+      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="16"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="73"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="38">
+        <v>25000</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="53"/>
+      <c r="K11" s="17">
+        <v>50</v>
+      </c>
+      <c r="L11" s="19"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="22"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="73"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="49">
+        <v>1800000</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="38">
+        <v>1000000</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="17">
+        <v>50</v>
+      </c>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="26"/>
+      <c r="W12" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="73"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="49">
+        <v>460000</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="38">
+        <v>500000</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="17">
+        <v>50</v>
+      </c>
+      <c r="L13" s="19"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="22"/>
+      <c r="W13" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="73"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="69">
+        <v>5100000</v>
+      </c>
+      <c r="E14" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="37">
+        <v>250000</v>
+      </c>
+      <c r="I14" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14">
+        <v>50</v>
+      </c>
+      <c r="L14" s="23"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="26"/>
+      <c r="W14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="73"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+      <c r="H15" s="38">
+        <v>25000</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="53"/>
+      <c r="K15" s="17">
+        <v>50</v>
+      </c>
+      <c r="L15" s="19"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="22"/>
+      <c r="W15" s="5"/>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="74"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="49">
+        <v>3600000</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" s="17">
+        <v>50</v>
+      </c>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="30"/>
+      <c r="W16" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="H20" s="75">
+        <f>SUM(H5:H15)</f>
+        <v>9050000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B8:B16"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="J4:J7"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E14:E15"/>
+  </mergeCells>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q16" xr:uid="{F258C04C-A4FA-4805-B174-3B4E93F9594B}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N16" xr:uid="{C4A7DBCA-C2D6-4FA5-982F-5A3428C7B505}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O16" xr:uid="{F127BD6B-DABA-4CD0-B7EC-5D6ADA771134}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M16" xr:uid="{0D926631-4967-407F-9CB9-1417932425E3}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16" xr:uid="{C1C18A2E-EA97-4EAA-BEB7-A7C718449DA8}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P16" xr:uid="{03233118-9D4D-48D3-8D64-4D826D3A4A45}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L16" xr:uid="{BA657230-24E8-4FBF-8E54-DAC070803EF0}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R16" xr:uid="{C66D08F0-1978-4285-8B45-EF57F48BC972}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S16" xr:uid="{D7824502-832B-4546-85D0-CDD293CA8C7E}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{C4FD8662-769B-494E-9138-E94D4C1D1E56}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{9A26C6CC-A90B-4470-9438-1D477C2A7711}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1619D449-50B6-4A9C-AD6A-E75333A47C33}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E7</xm:sqref>
+          <xm:sqref>E2:E4 E8:E9 E12:E14 E16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -745,204 +2029,198 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="52.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="76.5">
+      <c r="A2" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30.75">
+      <c r="A3" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="60.75">
+      <c r="A4" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="60.75">
+      <c r="A5" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="183">
+      <c r="A6" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="76.5">
+      <c r="A7" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="76.5">
+      <c r="A8" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="76.5">
+      <c r="A9" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="76.5">
+      <c r="A10" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="60.75">
+      <c r="A11" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="76.5">
+      <c r="A12" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="45.75">
+      <c r="A13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30.75">
+      <c r="A14" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="45.75">
+      <c r="A15" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="45.75">
+      <c r="A16" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="60.75">
+      <c r="A17" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="60.75">
+      <c r="A18" s="77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="152.25">
+      <c r="A19" s="77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="45.75">
+      <c r="A20" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="76.5">
+      <c r="A21" s="77" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8"/>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8"/>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="9"/>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="9"/>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="9"/>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="10"/>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="11"/>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="11"/>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
+      <c r="B21" s="79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="45.75">
+      <c r="A22" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -967,6 +2245,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1046,6 +2325,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1189,14 +2473,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Vitalie Vremis</DisplayName>
+        <AccountId>338</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBFBB887-5DC5-4CC5-B981-61FC103489AC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D518B4E-C20A-4FFC-BC13-992313191C2A}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E1EBA35-2B5F-4AEF-A4D2-B5ABF7D7A146}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C22A88-BD58-4ADE-9D27-BFDC07A9CF90}"/>
 </file>
--- a/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
@@ -1,15 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27321"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28627"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="280" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0951568A-30A6-4C89-BDC7-2AFB0687589C}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="980" documentId="11_0E84CF80AB4828E5C83BB2163A3B3130C40CB8FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7AEC56-28F1-4276-BC86-51F13443132A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="381" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects" sheetId="1" r:id="rId1"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId2"/>
+    <sheet name="Projects (3)" sheetId="6" r:id="rId1"/>
+    <sheet name="Projects (2.6)" sheetId="5" r:id="rId2"/>
+    <sheet name="Projects (2.5)" sheetId="4" r:id="rId3"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,6 +40,141 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={EB6D9F1D-1093-443D-9852-59A1AC744A33}</author>
+    <author>tc={DCF56ECC-FA71-46B4-8431-C6926AD78D1B}</author>
+    <author>tc={936BA648-9D7A-44C5-A1B1-668994676C0D}</author>
+    <author>tc={F6E347AD-C5A2-4313-AAB4-029A64DA333D}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{EB6D9F1D-1093-443D-9852-59A1AC744A33}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please select a category</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{DCF56ECC-FA71-46B4-8431-C6926AD78D1B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the baseline in terms of number of beneficiaires</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{936BA648-9D7A-44C5-A1B1-668994676C0D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the target in terms of number of beneficiaries target</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{F6E347AD-C5A2-4313-AAB4-029A64DA333D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please provide any assumption or comments on how you estimate the number of beneficiaries</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={847EDF1A-059F-485E-B308-899AE379E984}</author>
+    <author>tc={84509177-62CC-46F1-9485-5ACEA26EF867}</author>
+    <author>tc={7290C994-B72F-48C1-AD70-161A6BF1D8E0}</author>
+    <author>tc={CEE1B33D-8DDA-4116-A6CC-BB51E93271B1}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{847EDF1A-059F-485E-B308-899AE379E984}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please select a category</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{84509177-62CC-46F1-9485-5ACEA26EF867}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the baseline in terms of number of beneficiaires</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{7290C994-B72F-48C1-AD70-161A6BF1D8E0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the target in terms of number of beneficiaries target</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{CEE1B33D-8DDA-4116-A6CC-BB51E93271B1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please provide any assumption or comments on how you estimate the number of beneficiaries</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={79F7E377-464B-4355-8E8B-CFFF8248A927}</author>
+    <author>tc={0F069FF2-52A0-451E-9BD7-35B668F0A119}</author>
+    <author>tc={4186C70B-5858-4B55-AF8D-3B2912B099F8}</author>
+    <author>tc={3AE4744A-B021-44CC-BF20-99FED1F7E8C6}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{79F7E377-464B-4355-8E8B-CFFF8248A927}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please select a category</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{0F069FF2-52A0-451E-9BD7-35B668F0A119}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the baseline in terms of number of beneficiaires</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{4186C70B-5858-4B55-AF8D-3B2912B099F8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please insert the target in terms of number of beneficiaries target</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{3AE4744A-B021-44CC-BF20-99FED1F7E8C6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Please provide any assumption or comments on how you estimate the number of beneficiaries</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={C770F223-8A8B-42FA-9D91-BA1B0A4993EA}</author>
@@ -77,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="150">
   <si>
     <t>Project ID</t>
   </si>
@@ -142,105 +285,457 @@
     <t>Policy Population</t>
   </si>
   <si>
+    <t>00095405</t>
+  </si>
+  <si>
+    <t>EE in Public Buildings</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/projects/removing-barriers-increase-investment-energy-efficiency-public-buildings-ukraine-through-esco-modality-small-and-medium-sized</t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t>No. of Beneficaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key indicators: 
+1. The actual cumulative direct GHG emission reduction as of June 2024 was 16,052.48 tCO2e; estimated reduction over a 20-year period was 69,190.0 tCO2e  
+2. 24,164.16 MWh were saved cumulatively since the Project start, which exceeded the goals set as 2,346 MWh. The total capacity of solar power stations to be installed under ESCO-SPP contracts is 6.5 MW, and 1 MW of energy storage. This will allow hospitals and water facilities to have electricity even during blackouts. 
+3. With direct project support, USD 22,92 million of investment in energy efficiency in public buildings was achieved. 
+4. The total number of green jobs created by the project is 4,562: 4498 energy managers and 64 energy auditors were trained. </t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you please provide information for all the categories ? </t>
+  </si>
+  <si>
+    <t>001000157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotion of Human Security </t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/press-releases/undp-and-japan-deliver-high-power-autotransformers-ukraine-ensure-unbroken-energy-supplies-over-half-million-people</t>
+  </si>
+  <si>
+    <t>Electricity Access</t>
+  </si>
+  <si>
+    <t>-4 Autotransformers (2 installed, 2 upcoming)</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Non-VF</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/press-releases/japan-undp-deliver-equipment-secure-power-supply-over-55-million-ukrainians</t>
+  </si>
+  <si>
+    <t>-Transporation Support for 7 Autotransformers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 gas turbine for power generation </t>
+  </si>
+  <si>
+    <t>Winterization/Green Energy Recovery Programme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.undp.org/ukraine/projects/green-energy-recovery-programme-ukraine
+https://www.undp.org/ukraine/press-releases/gas-piston-cogeneration-units-delivered-odesa-undp-cover-45-citys-energy-needs-water-heating-and-sewage-services 
+</t>
+  </si>
+  <si>
+    <t>MW added</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Overall budget for Winterization and Green Energy Recovery Programme: USD 283,731,053.25
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FW Norway:	USD   9,892,766.50 
+South Korea:	USD   2,000,000.00 
+Iceland FW:	 USD  500,000.00 
+Sweden FW1:	USD   5,580,876.00 
+Sweden FW2:	USD   5,651,314.21 
+TRAC:	             USD    5,600.00 USD
+Denmark 1:	USD   10,967,269.51 
+SIDA:	              USD   32,357,281.93 
+Belgium: 	USD   9,646,302.24 
+NORAD 1:	USD   11,431,837.22 
+NORAD 2:	 USD  93,993,799.88 
+Japan:	              USD   70,000,000.00 
+Denmark 2:	USD   6,606,959.33 
+Germany:	 USD     4,000,000.00 
+European Commission:  USD 21,097,046.42
+Provided access to energy for 2,600,000 beneficiaries through delivery of 2 gas turbines for power generation in Ukraine with total capacity of 108 MW.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Provided access to energy for 450,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>beneficiaries through procurement of 13.4 MW of gas pistons and ongoing procurement of additional gas pistons with capacity of 16.5 MW.</t>
+    </r>
+  </si>
+  <si>
+    <t>Japan, Norway, Sweden</t>
+  </si>
+  <si>
+    <t>Procurement of 80 MW (8x10MW) of gas pistons with plans to increase to 160 MW, to benefit 900,955 beneficiaries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway </t>
+  </si>
+  <si>
+    <t>Provided access to energy for 630,000 beneficiaries through procurement of 90.6 MW of gas generation (10x1.5M, 2x3.3MW gas pistons and 15MW and 54 MW turbines).</t>
+  </si>
+  <si>
+    <t>Japan, Norway, Sweden, EU</t>
+  </si>
+  <si>
+    <t>Procurement of a gas booster compressor for restoring gas supply.</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Provided access to energy for 95,800 beneficiaries through procurement of 6.7 MW of gas generation and ongoing technical design services.</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Health services</t>
+  </si>
+  <si>
+    <t>Critical facilities supported (hospitals, schools, water pumps) and their user numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide access to clean energy, namely 0,2 MW of renewable energy through solar power installation for 1 hospital benefiting 10,700 people </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other </t>
+  </si>
+  <si>
+    <t>Number of municipalities/provinces receiving energy equipment</t>
+  </si>
+  <si>
+    <t>314 municipalities</t>
+  </si>
+  <si>
+    <t>Dedicated group of experts
+(more than 20) working directly in Ministry
+of Energy of Ukraine to support the
+coordination of energy equipment
+distribution between the Ministries and
+Municipalities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denmark </t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Restoration of critical utility services through the installation of co-generation equipment to ensure reliable heat, water, and sewage services during power outages (14MW)</t>
+  </si>
+  <si>
+    <t>Denmark, Sweden, Belgium</t>
+  </si>
+  <si>
+    <t>Support of in-kind donation 40 MW of generation</t>
+  </si>
+  <si>
+    <t>12MW gas turbine</t>
+  </si>
+  <si>
+    <t>SIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development of a digital platform Energy Programme Information Management System (EPIMS) to address integrated energy needs, facilitating immediate repair work on energy infrastructure and efficiently restore the energy sector. </t>
+  </si>
+  <si>
+    <t>Crisis response for securing reliable energy access in Ukraine (FPI Energy)</t>
+  </si>
+  <si>
+    <t>Restoration of critical utility services through the installation of co-generation equipment to ensure reliable heat, water, and sewage services during power outages, benefitting over 1.6 million residents (6.5 MW)</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>Provision of rooftop Solar Power Plants (SPP) 0.5 MW to ensure a stable and sustainable freshwater supply, reducing the city’s energy vulnerability and advancing long-term renewable energy goals</t>
+  </si>
+  <si>
+    <t>Construction of a Biomass Co-generation Power Plant namely 8 MW thermal and 2.2 MW electical</t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation of frequency drivers for electric motors of pumps, smoke extractors, and fans in boiler houses of the city </t>
+  </si>
+  <si>
     <t>Support to SDGs localization in Ukraine</t>
   </si>
   <si>
     <t>http://open.undp.org/projects/00099918</t>
   </si>
   <si>
-    <t xml:space="preserve">Can you please provide information for all the categories ? </t>
-  </si>
-  <si>
-    <t>EE in Public Buildings</t>
-  </si>
-  <si>
-    <t>PIMS+</t>
-  </si>
-  <si>
-    <t>001000157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promotion of Human Security </t>
-  </si>
-  <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
-    <t>Japan</t>
+    <t>Coordination of energy activities across UN entities and other international assistance projects to facilitate strategic alignment and effective implementation</t>
+  </si>
+  <si>
+    <t>Restoration of critical utility services through the installation of co-generation equipment to ensure reliable heat, water, and sewage services during power outages</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=4114</t>
   </si>
   <si>
     <t>Access to electricity (direct access to electricity, lighting, heating, cooling, etc)</t>
   </si>
   <si>
-    <t>https://www.undp.org/ukraine/press-releases/undp-and-japan-deliver-high-power-autotransformers-ukraine-ensure-unbroken-energy-supplies-over-half-million-people</t>
-  </si>
-  <si>
-    <t>No. of Beneficaries</t>
-  </si>
-  <si>
-    <t>-4 Autotransformers (2 installed, 2 upcoming)</t>
-  </si>
-  <si>
-    <t>https://www.undp.org/ukraine/press-releases/japan-undp-deliver-equipment-secure-power-supply-over-55-million-ukrainians</t>
-  </si>
-  <si>
-    <t>-Transporation Support for 7 Autotransformers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1 gas turbine for power generation </t>
-  </si>
-  <si>
     <t>00134106</t>
   </si>
   <si>
+    <t>Winterization/Energy Sector Recovery</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00147472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2 gas turbine for power generation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 gas compressor </t>
+  </si>
+  <si>
+    <t>-Transportation Support for 2 Autotransformers</t>
+  </si>
+  <si>
+    <t>-1 gas pistons power generation system</t>
+  </si>
+  <si>
+    <t>-25 bushings (750kV)</t>
+  </si>
+  <si>
+    <t>ROK</t>
+  </si>
+  <si>
+    <t>-15 bushings (330kV)</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>-1 Autotransformer (upcoming)</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.undp.org/ukraine/projects/green-energy-recovery-programme-ukraine
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Overall budget for Winterization and Green Energy Recovery Programme: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">244 846 904,36 USD:                                         
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FW Norway:	 9 892 766,50 USD
+South Korea:	 2 000 000,00 USD
+Iceland FW:	 500 000,00 USD
+Sweden FW1:	 5 580 876,00 USD
+Sweden FW2:	 5 651 314,21 USD
+TRAC:	               5 600,00 USD
+Denmark 1:	 10 967 269,50 USD
+SIDA:	               14 570 179,48 USD
+Belgium: 	 9 646 302,24 USD  
+NORAD 1:	 11 431 837,22 USD  
+NORAD 2:	 93 993 799,88 USD  
+Japan:	               70 000 000,00 USD  
+Denmark 2:	 6 606 959,34 USD  
+Germany:	 4 000 000,00 USD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+  </si>
+  <si>
+    <t>Provided access to energy for 2,600,000 beneficiaries through delivery of 2 gas turbines for power generation in Ukraine with total capacity of 108 MW.</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/ukraine/press-releases/gas-piston-cogeneration-units-delivered-odesa-undp-cover-45-citys-energy-needs-water-heating-and-sewage-services </t>
+  </si>
+  <si>
+    <t>Overall budget for Winterization and Green Energy Recovery Programme: 244 846 904,36 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy and Regulatory Framework </t>
+  </si>
+  <si>
+    <t>Provision of legislative support for the green energy transition, including distributed energy generation benefiting all population of Ukraine</t>
+  </si>
+  <si>
+    <t>Coordination of energy activities across UN entities and other international assistance projects to facilitate strategic alignment
+and effective implementation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Winterization/Energy Sector Recovery </t>
   </si>
   <si>
-    <t xml:space="preserve">-2 gas turbine for power generation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1 gas compressor </t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>-Transportation Support for 2 Autotransformers</t>
-  </si>
-  <si>
-    <t>-1 gas pistons power generation system</t>
-  </si>
-  <si>
-    <t>-25 bushings (750kV)</t>
-  </si>
-  <si>
-    <t>ROK</t>
-  </si>
-  <si>
-    <t>-15 bushings (330kV)</t>
-  </si>
-  <si>
-    <t>Iceland</t>
-  </si>
-  <si>
-    <t>-1 Autotransformer (upcoming)</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>TBC</t>
-  </si>
-  <si>
-    <t>Germany</t>
+    <t>https://www.undp.org/ukraine/projects/green-energy-recovery-programme-ukraine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Overall budget for Winterization and Green Energy Recovery Programme: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">244 846 904,36 USD:                                         
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FW Norway:	 9 892 766,50 USD
+South Korea:	 2 000 000,00 USD
+Iceland FW:	 500 000,00 USD
+Sweden FW1:	 5 580 876,00 USD
+Sweden FW2:	 5 651 314,21 USD
+TRAC:	               5 600,00 USD
+Denmark 1:	 10 967 269,50 USD
+SIDA:	               14 570 179,48 USD
+Belgium: 	 9 646 302,24 USD  
+NORAD 1:	 11 431 837,22 USD  
+NORAD 2:	 93 993 799,88 USD  
+Japan:	               70 000 000,00 USD  
+Denmark 2:	 6 606 959,34 USD  
+Germany:	 4 000 000,00 USD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
   </si>
   <si>
     <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t>Number of MW installed capacity</t>
   </si>
   <si>
@@ -286,13 +781,7 @@
     <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
   </si>
   <si>
-    <t>Energy Efficiency Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
-  </si>
-  <si>
-    <t>Energy Infrastructure Services</t>
   </si>
   <si>
     <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
@@ -359,10 +848,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,8 +908,77 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,8 +991,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -642,15 +1219,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -716,15 +1284,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -771,7 +1330,16 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="medium">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
@@ -780,21 +1348,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -861,117 +1425,409 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1289,6 +2145,57 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2023-11-14T00:24:52.08" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{EB6D9F1D-1093-443D-9852-59A1AC744A33}">
+    <text>Please select a category</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2023-11-14T00:24:31.19" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{DCF56ECC-FA71-46B4-8431-C6926AD78D1B}">
+    <text>Please insert the baseline in terms of number of beneficiaires</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2023-11-14T00:23:33.06" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{936BA648-9D7A-44C5-A1B1-668994676C0D}">
+    <text>Please insert the target in terms of number of beneficiaries target</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2023-11-14T00:25:34.71" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{F6E347AD-C5A2-4313-AAB4-029A64DA333D}">
+    <text>Please provide any assumption or comments on how you estimate the number of beneficiaries</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2023-11-14T00:24:52.08" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{847EDF1A-059F-485E-B308-899AE379E984}">
+    <text>Please select a category</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2023-11-14T00:24:31.19" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{84509177-62CC-46F1-9485-5ACEA26EF867}">
+    <text>Please insert the baseline in terms of number of beneficiaires</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2023-11-14T00:23:33.06" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{7290C994-B72F-48C1-AD70-161A6BF1D8E0}">
+    <text>Please insert the target in terms of number of beneficiaries target</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2023-11-14T00:25:34.71" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{CEE1B33D-8DDA-4116-A6CC-BB51E93271B1}">
+    <text>Please provide any assumption or comments on how you estimate the number of beneficiaries</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2023-11-14T00:24:52.08" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{79F7E377-464B-4355-8E8B-CFFF8248A927}">
+    <text>Please select a category</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2023-11-14T00:24:31.19" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{0F069FF2-52A0-451E-9BD7-35B668F0A119}">
+    <text>Please insert the baseline in terms of number of beneficiaires</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2023-11-14T00:23:33.06" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{4186C70B-5858-4B55-AF8D-3B2912B099F8}">
+    <text>Please insert the target in terms of number of beneficiaries target</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2023-11-14T00:25:34.71" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{3AE4744A-B021-44CC-BF20-99FED1F7E8C6}">
+    <text>Please provide any assumption or comments on how you estimate the number of beneficiaries</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E1" dT="2023-11-14T00:24:52.08" personId="{F9F8A88C-EB1D-4F7A-8948-61BA772610BE}" id="{C770F223-8A8B-42FA-9D91-BA1B0A4993EA}">
     <text>Please select a category</text>
   </threadedComment>
@@ -1305,36 +2212,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3386D416-537C-4C13-B214-8A7154AE5505}">
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" style="113" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="43.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="46" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32" t="s">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1349,677 +2266,973 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2">
-        <v>99918</v>
-      </c>
-      <c r="B2" s="33" t="s">
+    <row r="2" spans="1:23" s="101" customFormat="1" ht="129.75" customHeight="1">
+      <c r="A2" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="33">
-        <v>6817448</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="41"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="16"/>
-      <c r="W2" s="4" t="s">
+      <c r="C2" s="98" t="s">
         <v>23</v>
       </c>
+      <c r="D2" s="129">
+        <v>5480000</v>
+      </c>
+      <c r="E2" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="97">
+        <v>0</v>
+      </c>
+      <c r="H2" s="99">
+        <v>30204</v>
+      </c>
+      <c r="I2" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="97">
+        <v>63</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="21"/>
+      <c r="W2" s="102" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="17">
-        <v>4114</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="34">
-        <v>5480000</v>
-      </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="22"/>
-      <c r="W3" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="A3" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="159" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="162">
+        <v>40000000</v>
+      </c>
+      <c r="E3" s="149" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="36">
+        <v>1000000</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>50</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="13"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="15"/>
+      <c r="W3" s="110"/>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="63">
-        <v>40000000</v>
-      </c>
-      <c r="E4" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="26"/>
-      <c r="W4" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="A4" s="157"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="196" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="163"/>
+      <c r="E4" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="36">
+        <v>1500000</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="166"/>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="15"/>
+      <c r="W4" s="110"/>
     </row>
     <row r="5" spans="1:23">
-      <c r="A5" s="61"/>
-      <c r="B5" s="58"/>
-      <c r="C5" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="55"/>
+      <c r="A5" s="158"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="29" t="s">
+        <v>38</v>
+      </c>
       <c r="F5" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0</v>
+      </c>
+      <c r="H5" s="37">
+        <v>1500000</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="167"/>
+      <c r="K5" s="16">
+        <v>50</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="21"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="21"/>
+      <c r="W5" s="110"/>
+    </row>
+    <row r="6" spans="1:23" ht="361.5" customHeight="1">
+      <c r="A6" s="95">
+        <v>134106</v>
+      </c>
+      <c r="B6" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="131">
+        <v>64600000</v>
+      </c>
+      <c r="E6" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="83">
+        <v>0</v>
+      </c>
+      <c r="H6" s="150">
+        <v>2600000</v>
+      </c>
+      <c r="I6" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="54">
+        <v>50</v>
+      </c>
+      <c r="L6" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+    </row>
+    <row r="7" spans="1:23" ht="60.75">
+      <c r="A7" s="95"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="112">
+        <v>16700000</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="83">
+        <v>0</v>
+      </c>
+      <c r="H7" s="87">
+        <v>450000</v>
+      </c>
+      <c r="I7" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="54">
+        <v>50</v>
+      </c>
+      <c r="L7" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+    </row>
+    <row r="8" spans="1:23" ht="60" customHeight="1">
+      <c r="A8" s="95"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="112">
+        <v>63352000</v>
+      </c>
+      <c r="E8" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="83">
+        <v>0</v>
+      </c>
+      <c r="H8" s="87">
+        <v>900955</v>
+      </c>
+      <c r="I8" s="90" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="54">
+        <v>50</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+    </row>
+    <row r="9" spans="1:23" ht="60.75">
+      <c r="A9" s="95"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="112">
+        <f>11915000+5164000+16500000+11000000</f>
+        <v>44579000</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="83">
+        <v>0</v>
+      </c>
+      <c r="H9" s="87">
+        <v>630000</v>
+      </c>
+      <c r="I9" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="54">
+        <v>50</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+    </row>
+    <row r="10" spans="1:23" ht="30.75">
+      <c r="A10" s="95"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="112">
+        <v>16500000</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="83">
+        <v>0</v>
+      </c>
+      <c r="H10" s="130">
+        <v>0</v>
+      </c>
+      <c r="I10" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="54">
+        <v>50</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+    </row>
+    <row r="11" spans="1:23" ht="70.5" customHeight="1">
+      <c r="A11" s="95"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="112">
+        <v>6119665.5300000003</v>
+      </c>
+      <c r="E11" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="83">
+        <v>0</v>
+      </c>
+      <c r="H11" s="87">
+        <v>95800</v>
+      </c>
+      <c r="I11" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="54">
+        <v>50</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+    </row>
+    <row r="12" spans="1:23" ht="76.5">
+      <c r="A12" s="95"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="112">
+        <v>5000000</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="83">
+        <v>0</v>
+      </c>
+      <c r="H12" s="89">
+        <v>1</v>
+      </c>
+      <c r="I12" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="54">
+        <v>50</v>
+      </c>
+      <c r="L12" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="37">
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+    </row>
+    <row r="13" spans="1:23" ht="91.5">
+      <c r="A13" s="95"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="112">
+        <v>1220931.3999999999</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="83">
+        <v>0</v>
+      </c>
+      <c r="H13" s="155" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="54">
+        <v>50</v>
+      </c>
+      <c r="L13" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="54"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+    </row>
+    <row r="14" spans="1:23" ht="60.75">
+      <c r="A14" s="116"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="114">
+        <v>10400000</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="118">
+        <v>0</v>
+      </c>
+      <c r="H14" s="151">
+        <v>14</v>
+      </c>
+      <c r="I14" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="54">
+        <v>50</v>
+      </c>
+      <c r="L14" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="122"/>
+      <c r="P14" s="122"/>
+      <c r="Q14" s="122"/>
+      <c r="R14" s="122"/>
+      <c r="S14" s="122"/>
+      <c r="T14" s="122"/>
+      <c r="U14" s="122"/>
+    </row>
+    <row r="15" spans="1:23" ht="30.75">
+      <c r="A15" s="95"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="115">
+        <v>15882409.9</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="118">
+        <v>0</v>
+      </c>
+      <c r="H15" s="152">
+        <v>40</v>
+      </c>
+      <c r="I15" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="54">
+        <v>50</v>
+      </c>
+      <c r="L15" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="122"/>
+      <c r="T15" s="122"/>
+      <c r="U15" s="122"/>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="139"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="144">
+        <v>17280000</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="83">
+        <v>0</v>
+      </c>
+      <c r="H16" s="153">
+        <v>12</v>
+      </c>
+      <c r="I16" s="143" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" s="54">
+        <v>50</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="122"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="122"/>
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="122"/>
+      <c r="S16" s="122"/>
+      <c r="T16" s="122"/>
+      <c r="U16" s="122"/>
+    </row>
+    <row r="17" spans="1:21" ht="91.5">
+      <c r="A17" s="116"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="138">
         <v>1000000</v>
       </c>
-      <c r="I5" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="52"/>
-      <c r="K5">
-        <v>50</v>
-      </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="16"/>
-      <c r="W5" s="5"/>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" s="61"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="37">
-        <v>1500000</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="52"/>
-      <c r="K6">
-        <v>50</v>
-      </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="16"/>
-      <c r="W6" s="5"/>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="62"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="17">
-        <v>0</v>
-      </c>
-      <c r="H7" s="38">
-        <v>1500000</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="53"/>
-      <c r="K7" s="17">
-        <v>50</v>
-      </c>
-      <c r="L7" s="19"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="22"/>
-      <c r="W7" s="5"/>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" s="72" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="49">
-        <v>64600000</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="17">
-        <v>0</v>
-      </c>
-      <c r="H8" s="38">
-        <v>2500000</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="17">
-        <v>50</v>
-      </c>
-      <c r="L8" s="27"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="30"/>
-      <c r="W8" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" s="73"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="66">
-        <v>9600000</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="37">
-        <v>250000</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="51" t="s">
+      <c r="E17" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="142">
+        <v>0</v>
+      </c>
+      <c r="H17" s="119">
+        <v>35800000</v>
+      </c>
+      <c r="I17" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="54">
+        <v>50</v>
+      </c>
+      <c r="L17" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="K9">
-        <v>50</v>
-      </c>
-      <c r="L9" s="23"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="26"/>
-      <c r="W9" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" s="73"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="37">
-        <v>500000</v>
-      </c>
-      <c r="I10" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="52"/>
-      <c r="K10">
-        <v>50</v>
-      </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="16"/>
-      <c r="W10" s="5"/>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" s="73"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="17">
-        <v>0</v>
-      </c>
-      <c r="H11" s="38">
-        <v>25000</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="17">
-        <v>50</v>
-      </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="22"/>
-      <c r="W11" s="5"/>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" s="73"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="49">
-        <v>1800000</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="38">
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="122"/>
+    </row>
+    <row r="18" spans="1:21" ht="76.5">
+      <c r="A18" s="122">
+        <v>1003605</v>
+      </c>
+      <c r="B18" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="122"/>
+      <c r="D18" s="147">
+        <f>6772151.9+241257.912</f>
+        <v>7013409.8120000008</v>
+      </c>
+      <c r="E18" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="122">
+        <v>0</v>
+      </c>
+      <c r="H18" s="154">
+        <v>6.5</v>
+      </c>
+      <c r="I18" s="146" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="122">
+        <v>50</v>
+      </c>
+      <c r="L18" s="125" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+    </row>
+    <row r="19" spans="1:21" ht="76.5">
+      <c r="A19" s="122"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="147">
+        <f>1244756.78+241257.912</f>
+        <v>1486014.692</v>
+      </c>
+      <c r="E19" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="122">
+        <v>0</v>
+      </c>
+      <c r="H19" s="147">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="54">
+        <v>50</v>
+      </c>
+      <c r="L19" s="126" t="s">
+        <v>41</v>
+      </c>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+    </row>
+    <row r="20" spans="1:21" ht="45.75">
+      <c r="A20" s="122"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="147">
+        <f>7543903.56+241257.912</f>
+        <v>7785161.4719999991</v>
+      </c>
+      <c r="E20" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="122" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="122">
+        <v>0</v>
+      </c>
+      <c r="H20" s="154">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I20" s="146" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="122">
+        <v>50</v>
+      </c>
+      <c r="L20" s="125" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+    </row>
+    <row r="21" spans="1:21" ht="45.75">
+      <c r="A21" s="126"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="148">
+        <f>4571202.53+241257.912</f>
+        <v>4812460.4419999998</v>
+      </c>
+      <c r="E21" s="197" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="54">
+        <v>0</v>
+      </c>
+      <c r="H21" s="148">
         <v>1000000</v>
       </c>
-      <c r="I12" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="17">
-        <v>50</v>
-      </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="26"/>
-      <c r="W12" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13" s="73"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="49">
-        <v>460000</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="17">
-        <v>0</v>
-      </c>
-      <c r="H13" s="38">
-        <v>500000</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="17">
-        <v>50</v>
-      </c>
-      <c r="L13" s="19"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="22"/>
-      <c r="W13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="A14" s="73"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="69">
-        <v>5100000</v>
-      </c>
-      <c r="E14" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="37">
-        <v>250000</v>
-      </c>
-      <c r="I14" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14">
-        <v>50</v>
-      </c>
-      <c r="L14" s="23"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="26"/>
-      <c r="W14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
-      <c r="A15" s="73"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="38">
-        <v>25000</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="53"/>
-      <c r="K15" s="17">
-        <v>50</v>
-      </c>
-      <c r="L15" s="19"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="22"/>
-      <c r="W15" s="5"/>
-    </row>
-    <row r="16" spans="1:23">
-      <c r="A16" s="74"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="49">
-        <v>3600000</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="17">
-        <v>0</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="K16" s="17">
-        <v>50</v>
-      </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="30"/>
-      <c r="W16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="6"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="H20" s="75">
-        <f>SUM(H5:H15)</f>
-        <v>9050000</v>
-      </c>
+      <c r="I21" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="54">
+        <v>50</v>
+      </c>
+      <c r="L21" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="134"/>
+      <c r="N21" s="122"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="122"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="122"/>
+      <c r="S21" s="122"/>
+      <c r="T21" s="122"/>
+      <c r="U21" s="122"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="136"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
+      <c r="M22" s="132"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="136"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="137"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="A8:A16"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="E14:E15"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="J3:J5"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q16" xr:uid="{F258C04C-A4FA-4805-B174-3B4E93F9594B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q5" xr:uid="{B9CE223C-D920-4AE0-86A8-D3E8C7727CD1}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N16" xr:uid="{C4A7DBCA-C2D6-4FA5-982F-5A3428C7B505}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N5" xr:uid="{3DFE4CFC-0315-4A49-A152-BD07F131B90F}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O16" xr:uid="{F127BD6B-DABA-4CD0-B7EC-5D6ADA771134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O5" xr:uid="{16628657-E224-4BD2-99C4-F79346AF8521}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M16" xr:uid="{0D926631-4967-407F-9CB9-1417932425E3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M5" xr:uid="{7B796153-E3F7-427B-94AD-2AADAF309E51}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T16" xr:uid="{C1C18A2E-EA97-4EAA-BEB7-A7C718449DA8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T5" xr:uid="{78A97FFD-D681-4BE4-8441-9D36C7ADAF80}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P16" xr:uid="{03233118-9D4D-48D3-8D64-4D826D3A4A45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P5" xr:uid="{BF8B553D-D756-40EC-9373-D871CEACD29F}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L16" xr:uid="{BA657230-24E8-4FBF-8E54-DAC070803EF0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L5" xr:uid="{AFC8DD14-6B8A-4766-839A-9C12BBDA4019}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R16" xr:uid="{C66D08F0-1978-4285-8B45-EF57F48BC972}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R5" xr:uid="{1DEE34A2-BDC6-4D6D-88AD-0FB2AD930E7A}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S16" xr:uid="{D7824502-832B-4546-85D0-CDD293CA8C7E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S5" xr:uid="{498F53CD-B01E-4861-8FBF-956C2417968A}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C6" r:id="rId2" xr:uid="{C4FD8662-769B-494E-9138-E94D4C1D1E56}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{9A26C6CC-A90B-4470-9438-1D477C2A7711}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{A3640FC6-8BEE-441D-B169-DCC2F5B35731}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{7328DDB3-AF63-45CF-B10D-7F70210728DD}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{9A48B76B-9FF5-4790-A30C-AD22DC4AC900}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
   <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1619D449-50B6-4A9C-AD6A-E75333A47C33}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EDBC991B-4CFD-4B36-90CD-367ACBB6EADC}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E4 E8:E9 E12:E14 E16</xm:sqref>
+          <xm:sqref>E2:E3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2028,189 +3241,3705 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2D4D6E-E9E5-4631-8904-F5C883848A7D}">
+  <dimension ref="A1:W25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" style="113" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="46" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="127" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="27" customHeight="1">
+      <c r="A2" s="101">
+        <v>99918</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="108" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="128">
+        <v>6817448</v>
+      </c>
+      <c r="I2" s="39"/>
+      <c r="J2" s="51"/>
+      <c r="L2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="15"/>
+      <c r="W2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="101" customFormat="1" ht="129.75" customHeight="1">
+      <c r="A3" s="124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="98" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="129">
+        <v>5480000</v>
+      </c>
+      <c r="E3" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="97">
+        <v>0</v>
+      </c>
+      <c r="H3" s="99">
+        <v>30204</v>
+      </c>
+      <c r="I3" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="97">
+        <v>63</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="21"/>
+      <c r="W3" s="102" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="159" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="162">
+        <v>40000000</v>
+      </c>
+      <c r="E4" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="36">
+        <v>1000000</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="15"/>
+      <c r="W4" s="110"/>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="157"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="109" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="163"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36">
+        <v>1500000</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="166"/>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="15"/>
+      <c r="W5" s="110"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="158"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="164"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1500000</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="167"/>
+      <c r="K6" s="16">
+        <v>50</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="21"/>
+      <c r="W6" s="110"/>
+    </row>
+    <row r="7" spans="1:23" ht="361.5" customHeight="1">
+      <c r="A7" s="95">
+        <v>134106</v>
+      </c>
+      <c r="B7" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="131">
+        <v>64600000</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="83">
+        <v>0</v>
+      </c>
+      <c r="H7" s="85">
+        <v>2600000</v>
+      </c>
+      <c r="I7" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="54">
+        <v>50</v>
+      </c>
+      <c r="L7" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+    </row>
+    <row r="8" spans="1:23" ht="57">
+      <c r="A8" s="95"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="112">
+        <v>16700000</v>
+      </c>
+      <c r="E8" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="83">
+        <v>0</v>
+      </c>
+      <c r="H8" s="87">
+        <v>450000</v>
+      </c>
+      <c r="I8" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="54">
+        <v>50</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+    </row>
+    <row r="9" spans="1:23" ht="60" customHeight="1">
+      <c r="A9" s="95"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="112">
+        <v>63352000</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="83">
+        <v>0</v>
+      </c>
+      <c r="H9" s="89">
+        <v>900955</v>
+      </c>
+      <c r="I9" s="90" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="54">
+        <v>50</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+    </row>
+    <row r="10" spans="1:23" ht="57">
+      <c r="A10" s="95"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="112">
+        <f>11915000+5164000+16500000+11000000</f>
+        <v>44579000</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="83">
+        <v>0</v>
+      </c>
+      <c r="H10" s="87">
+        <v>630000</v>
+      </c>
+      <c r="I10" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="54">
+        <v>50</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+    </row>
+    <row r="11" spans="1:23" ht="28.5">
+      <c r="A11" s="95"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="112">
+        <v>16500000</v>
+      </c>
+      <c r="E11" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="83">
+        <v>0</v>
+      </c>
+      <c r="H11" s="130">
+        <v>0</v>
+      </c>
+      <c r="I11" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="54">
+        <v>50</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+    </row>
+    <row r="12" spans="1:23" ht="48.75" customHeight="1">
+      <c r="A12" s="95"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="112">
+        <v>6119665.5300000003</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="83">
+        <v>0</v>
+      </c>
+      <c r="H12" s="89">
+        <v>95800</v>
+      </c>
+      <c r="I12" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="54">
+        <v>50</v>
+      </c>
+      <c r="L12" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+    </row>
+    <row r="13" spans="1:23" ht="42.75">
+      <c r="A13" s="95"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="112">
+        <v>5000000</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="83">
+        <v>0</v>
+      </c>
+      <c r="H13" s="89">
+        <v>10700</v>
+      </c>
+      <c r="I13" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="54">
+        <v>50</v>
+      </c>
+      <c r="L13" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="54"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+    </row>
+    <row r="14" spans="1:23" ht="85.5">
+      <c r="A14" s="95"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="112">
+        <v>1170931.3700000001</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="83">
+        <v>0</v>
+      </c>
+      <c r="H14" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I14" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="54">
+        <v>50</v>
+      </c>
+      <c r="L14" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+    </row>
+    <row r="15" spans="1:23" ht="57">
+      <c r="A15" s="95"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="112">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="83">
+        <v>0</v>
+      </c>
+      <c r="H15" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I15" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="54">
+        <v>50</v>
+      </c>
+      <c r="L15" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+    </row>
+    <row r="16" spans="1:23" ht="57">
+      <c r="A16" s="116"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="114">
+        <v>10400000</v>
+      </c>
+      <c r="E16" s="118" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="118">
+        <v>0</v>
+      </c>
+      <c r="H16" s="121">
+        <v>1600000</v>
+      </c>
+      <c r="I16" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="54">
+        <v>50</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="122"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="122"/>
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="122"/>
+      <c r="S16" s="122"/>
+      <c r="T16" s="122"/>
+      <c r="U16" s="122"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="95"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="115">
+        <v>15882409.9</v>
+      </c>
+      <c r="E17" s="118" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="118">
+        <v>0</v>
+      </c>
+      <c r="H17" s="115">
+        <v>250000</v>
+      </c>
+      <c r="I17" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="J17" s="123" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="54">
+        <v>50</v>
+      </c>
+      <c r="L17" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="122"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="139"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="144">
+        <v>17280000</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="83">
+        <v>0</v>
+      </c>
+      <c r="H18" s="145">
+        <v>260000</v>
+      </c>
+      <c r="I18" s="143" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="54">
+        <v>50</v>
+      </c>
+      <c r="L18" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="122"/>
+      <c r="T18" s="122"/>
+      <c r="U18" s="122"/>
+    </row>
+    <row r="19" spans="1:21" ht="71.25">
+      <c r="A19" s="116"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="138">
+        <v>1000000</v>
+      </c>
+      <c r="E19" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="142">
+        <v>0</v>
+      </c>
+      <c r="H19" s="119">
+        <v>35800000</v>
+      </c>
+      <c r="I19" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="54">
+        <v>50</v>
+      </c>
+      <c r="L19" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M19" s="122"/>
+      <c r="N19" s="122"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="122"/>
+      <c r="Q19" s="122"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="122"/>
+      <c r="T19" s="122"/>
+      <c r="U19" s="122"/>
+    </row>
+    <row r="20" spans="1:21" ht="57">
+      <c r="A20" s="122">
+        <v>1003605</v>
+      </c>
+      <c r="B20" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="122"/>
+      <c r="D20" s="147">
+        <f>6772151.9+241257.912</f>
+        <v>7013409.8120000008</v>
+      </c>
+      <c r="E20" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="122">
+        <v>0</v>
+      </c>
+      <c r="H20" s="147">
+        <v>1600000</v>
+      </c>
+      <c r="I20" s="146" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="122">
+        <v>50</v>
+      </c>
+      <c r="L20" s="125" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+    </row>
+    <row r="21" spans="1:21" ht="57">
+      <c r="A21" s="122"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="147">
+        <f>1244756.78+241257.912</f>
+        <v>1486014.692</v>
+      </c>
+      <c r="E21" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="122">
+        <v>0</v>
+      </c>
+      <c r="H21" s="147">
+        <v>440000</v>
+      </c>
+      <c r="I21" s="146" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="54">
+        <v>50</v>
+      </c>
+      <c r="L21" s="126" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+    </row>
+    <row r="22" spans="1:21" ht="28.5">
+      <c r="A22" s="122"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="147">
+        <f>7543903.56+241257.912</f>
+        <v>7785161.4719999991</v>
+      </c>
+      <c r="E22" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="122" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="122">
+        <v>0</v>
+      </c>
+      <c r="H22" s="147">
+        <v>15000</v>
+      </c>
+      <c r="I22" s="146" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="122">
+        <v>50</v>
+      </c>
+      <c r="L22" s="125" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+    </row>
+    <row r="23" spans="1:21" ht="42.75">
+      <c r="A23" s="126"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="148">
+        <f>4571202.53+241257.912</f>
+        <v>4812460.4419999998</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="54">
+        <v>0</v>
+      </c>
+      <c r="H23" s="148">
+        <v>1000000</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="54">
+        <v>50</v>
+      </c>
+      <c r="L23" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="134"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="122"/>
+      <c r="P23" s="122"/>
+      <c r="Q23" s="122"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="122"/>
+      <c r="T23" s="122"/>
+      <c r="U23" s="122"/>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="136"/>
+      <c r="B24" s="136"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="137"/>
+      <c r="M24" s="132"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="136"/>
+      <c r="B25" s="136"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="J4:J6"/>
+  </mergeCells>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6" xr:uid="{B48D2286-9F63-4D9C-A81D-EBB16F66AF69}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{BE6A08E0-A0CE-4E0D-B689-FF0C4E6BBD8C}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L6" xr:uid="{457114F9-FCC9-43F4-A8AB-F105FCBD2FE3}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P6" xr:uid="{5215DA8C-828B-4C0F-8628-60DF408AE90B}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T6" xr:uid="{F6671A87-19EF-4D3D-81D3-3024142733F5}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M6" xr:uid="{B3D24614-501F-4F10-84CE-97664D0ED7C0}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O6" xr:uid="{F021DF6E-DA90-43E7-AB29-B235C07C4B83}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N6" xr:uid="{731658AC-ACFF-4B33-A896-802BBFEE0DC8}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6" xr:uid="{A43E17A1-D645-4A04-B2B5-C57D07C2D3D7}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{128D755E-8010-445E-AD3C-8540A7E4A9D7}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{302E2BCB-4FF1-44A0-9E52-9D2325DF9815}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{B4E14392-BD70-4D9A-A766-CE36FF7441EC}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{A7785126-C2CB-48C2-B167-B49922099AA3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{252FFC09-5ABD-40A1-9A73-E0571E8BBE3F}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0594403-2DBB-4117-9863-F1CDBAB9D9FB}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="46" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="27" customHeight="1">
+      <c r="A2" s="101">
+        <v>99918</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="32">
+        <v>6817448</v>
+      </c>
+      <c r="I2" s="39"/>
+      <c r="J2" s="51"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="15"/>
+      <c r="W2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" s="101" customFormat="1" ht="129.75" customHeight="1">
+      <c r="A3" s="97">
+        <v>4114</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="98" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="29">
+        <v>5480000</v>
+      </c>
+      <c r="E3" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="97">
+        <v>0</v>
+      </c>
+      <c r="H3" s="99">
+        <v>30204</v>
+      </c>
+      <c r="I3" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="97">
+        <v>63</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="21"/>
+      <c r="W3" s="102" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="159" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="175">
+        <v>40000000</v>
+      </c>
+      <c r="E4" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="36">
+        <v>1000000</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="15"/>
+      <c r="W4" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="173"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="176"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36">
+        <v>1500000</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="166"/>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="15"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1500000</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="167"/>
+      <c r="K6" s="16">
+        <v>50</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="21"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="178" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="171" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="72">
+        <v>64600000</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="73">
+        <v>0</v>
+      </c>
+      <c r="H7" s="75">
+        <v>2500000</v>
+      </c>
+      <c r="I7" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="16">
+        <v>50</v>
+      </c>
+      <c r="L7" s="26"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="29"/>
+      <c r="W7" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="179"/>
+      <c r="B8" s="180"/>
+      <c r="C8" s="181"/>
+      <c r="D8" s="182">
+        <v>9600000</v>
+      </c>
+      <c r="E8" s="171" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="78">
+        <v>0</v>
+      </c>
+      <c r="H8" s="79">
+        <v>250000</v>
+      </c>
+      <c r="I8" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="165" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8" s="22"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="25"/>
+      <c r="W8" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="179"/>
+      <c r="B9" s="180"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="180"/>
+      <c r="F9" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="78">
+        <v>0</v>
+      </c>
+      <c r="H9" s="79">
+        <v>500000</v>
+      </c>
+      <c r="I9" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="166"/>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="15"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="179"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="172"/>
+      <c r="F10" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="73">
+        <v>0</v>
+      </c>
+      <c r="H10" s="75">
+        <v>25000</v>
+      </c>
+      <c r="I10" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="167"/>
+      <c r="K10" s="16">
+        <v>50</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="21"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="179"/>
+      <c r="B11" s="180"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="72">
+        <v>1800000</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="73">
+        <v>0</v>
+      </c>
+      <c r="H11" s="75">
+        <v>1000000</v>
+      </c>
+      <c r="I11" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="16">
+        <v>50</v>
+      </c>
+      <c r="L11" s="22"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="25"/>
+      <c r="W11" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="179"/>
+      <c r="B12" s="180"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="72">
+        <v>460000</v>
+      </c>
+      <c r="E12" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="73">
+        <v>0</v>
+      </c>
+      <c r="H12" s="75">
+        <v>500000</v>
+      </c>
+      <c r="I12" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="16">
+        <v>50</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="21"/>
+      <c r="W12" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="179"/>
+      <c r="B13" s="180"/>
+      <c r="C13" s="168"/>
+      <c r="D13" s="169">
+        <v>5100000</v>
+      </c>
+      <c r="E13" s="171" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="78">
+        <v>0</v>
+      </c>
+      <c r="H13" s="79">
+        <v>250000</v>
+      </c>
+      <c r="I13" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="165" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13">
+        <v>50</v>
+      </c>
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="25"/>
+      <c r="W13" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="179"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="168"/>
+      <c r="D14" s="170"/>
+      <c r="E14" s="172"/>
+      <c r="F14" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="73">
+        <v>0</v>
+      </c>
+      <c r="H14" s="75">
+        <v>25000</v>
+      </c>
+      <c r="I14" s="76" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="167"/>
+      <c r="K14" s="16">
+        <v>50</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="21"/>
+      <c r="W14" s="5"/>
+    </row>
+    <row r="15" spans="1:23" ht="18" customHeight="1">
+      <c r="A15" s="179"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="81">
+        <v>3600000</v>
+      </c>
+      <c r="E15" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="78">
+        <v>0</v>
+      </c>
+      <c r="H15" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="82"/>
+      <c r="J15" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15">
+        <v>50</v>
+      </c>
+      <c r="L15" s="63"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="65"/>
+      <c r="W15" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="210.4" customHeight="1">
+      <c r="A16" s="95">
+        <v>134106</v>
+      </c>
+      <c r="B16" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="83">
+        <v>0</v>
+      </c>
+      <c r="H16" s="85">
+        <v>2600000</v>
+      </c>
+      <c r="I16" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="54">
+        <v>50</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+    </row>
+    <row r="17" spans="1:21" ht="71.25">
+      <c r="A17" s="95"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="83">
+        <v>0</v>
+      </c>
+      <c r="H17" s="87">
+        <v>450000</v>
+      </c>
+      <c r="I17" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="54">
+        <v>50</v>
+      </c>
+      <c r="L17" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+    </row>
+    <row r="18" spans="1:21" ht="60" customHeight="1">
+      <c r="A18" s="95"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="83">
+        <v>0</v>
+      </c>
+      <c r="H18" s="89">
+        <v>900955</v>
+      </c>
+      <c r="I18" s="90" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="54">
+        <v>50</v>
+      </c>
+      <c r="L18" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+    </row>
+    <row r="19" spans="1:21" ht="57">
+      <c r="A19" s="95"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="83">
+        <v>0</v>
+      </c>
+      <c r="H19" s="91">
+        <v>630000</v>
+      </c>
+      <c r="I19" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="54">
+        <v>50</v>
+      </c>
+      <c r="L19" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+    </row>
+    <row r="20" spans="1:21" ht="28.5">
+      <c r="A20" s="95"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="83">
+        <v>0</v>
+      </c>
+      <c r="H20" s="93">
+        <v>0</v>
+      </c>
+      <c r="I20" s="94" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="54">
+        <v>50</v>
+      </c>
+      <c r="L20" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+    </row>
+    <row r="21" spans="1:21" ht="48.75" customHeight="1">
+      <c r="A21" s="95"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="83">
+        <v>0</v>
+      </c>
+      <c r="H21" s="89">
+        <v>95800</v>
+      </c>
+      <c r="I21" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="54">
+        <v>50</v>
+      </c>
+      <c r="L21" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+    </row>
+    <row r="22" spans="1:21" ht="42.75">
+      <c r="A22" s="95"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="83">
+        <v>0</v>
+      </c>
+      <c r="H22" s="89">
+        <v>10700</v>
+      </c>
+      <c r="I22" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="54">
+        <v>50</v>
+      </c>
+      <c r="L22" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+    </row>
+    <row r="23" spans="1:21" ht="56.25" customHeight="1">
+      <c r="A23" s="95"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="83">
+        <v>0</v>
+      </c>
+      <c r="H23" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I23" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="58"/>
+      <c r="K23" s="54">
+        <v>50</v>
+      </c>
+      <c r="L23" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+    </row>
+    <row r="24" spans="1:21" ht="85.5">
+      <c r="A24" s="95"/>
+      <c r="B24" s="96"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="83">
+        <v>0</v>
+      </c>
+      <c r="H24" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I24" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" s="54">
+        <v>50</v>
+      </c>
+      <c r="L24" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+    </row>
+    <row r="25" spans="1:21" ht="57">
+      <c r="A25" s="95"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="83">
+        <v>0</v>
+      </c>
+      <c r="H25" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I25" s="86" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="54">
+        <v>50</v>
+      </c>
+      <c r="L25" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+    </row>
+    <row r="26" spans="1:21" ht="71.25">
+      <c r="A26" s="95"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="83">
+        <v>0</v>
+      </c>
+      <c r="H26" s="85">
+        <v>35800000</v>
+      </c>
+      <c r="I26" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K26" s="54">
+        <v>50</v>
+      </c>
+      <c r="L26" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="54"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="B7:B15"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="J13:J14"/>
+  </mergeCells>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q15" xr:uid="{96B94D81-BA59-4531-9DFE-24D5F9CE9353}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N15" xr:uid="{8AC1D835-08B6-4B14-B02C-BD1DA656F966}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O15" xr:uid="{0C66A12B-E237-4C49-84DE-FC998659A101}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M15" xr:uid="{8C6DEF7E-F3D9-48ED-AE6B-65B7ACB9F37B}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T15" xr:uid="{1D60A039-E62C-4102-A94A-25D77DCFAECA}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P15" xr:uid="{8AF9DD93-CB32-4D87-9533-356ECE7ABAFE}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L15" xr:uid="{84FD91F0-A81E-45B6-820A-4C9D6750C6A4}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R15" xr:uid="{1B01A017-E0ED-4DB7-83AC-157E8DB1B1E7}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S15" xr:uid="{7AE4BA3D-E214-4934-A68B-0E2BE7B62553}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{75DF0C91-B1E8-47B5-80C2-AE6D1FDC07B8}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{F891CEED-4FD3-4471-98F3-049993D58CF1}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{6670C315-1A26-46D6-9168-6F2FA212FF43}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{5054A6EC-12F3-44AF-BA23-BEE3B73DF0B5}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{D71F9A62-9284-4EC2-BFF1-6B4744462081}"/>
+    <hyperlink ref="C17" r:id="rId6" xr:uid="{47974951-F9A5-436B-A5F1-6298BAD2CC05}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D77DBCA2-DA6D-4C08-8F0A-A8F3D8395D00}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E7:E8 E11:E13 E15 E2:E4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W26"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="46" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="20" max="20" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>99918</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="32">
+        <v>6817448</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="51"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="15"/>
+      <c r="W2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="129.75" customHeight="1">
+      <c r="A3" s="16">
+        <v>4114</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="33">
+        <v>5480000</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="17">
+        <v>0</v>
+      </c>
+      <c r="H3" s="48">
+        <v>30204</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="16">
+        <v>63</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="21"/>
+      <c r="W3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="159" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="175">
+        <v>40000000</v>
+      </c>
+      <c r="E4" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="36">
+        <v>1000000</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="165" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="15"/>
+      <c r="W4" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="173"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="176"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36">
+        <v>1500000</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="166"/>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="15"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0</v>
+      </c>
+      <c r="H6" s="37">
+        <v>1500000</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="167"/>
+      <c r="K6" s="16">
+        <v>50</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="21"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="185" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="193" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="43">
+        <v>64600000</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="37">
+        <v>2500000</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="16">
+        <v>50</v>
+      </c>
+      <c r="L7" s="26"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="29"/>
+      <c r="W7" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="186"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="187">
+        <v>9600000</v>
+      </c>
+      <c r="E8" s="193" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="36">
+        <v>250000</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="165" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8" s="22"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="25"/>
+      <c r="W8" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="186"/>
+      <c r="B9" s="194"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="188"/>
+      <c r="E9" s="194"/>
+      <c r="F9" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="36">
+        <v>500000</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="166"/>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="15"/>
+      <c r="W9" s="5"/>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="186"/>
+      <c r="B10" s="194"/>
+      <c r="C10" s="198"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0</v>
+      </c>
+      <c r="H10" s="37">
+        <v>25000</v>
+      </c>
+      <c r="I10" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="167"/>
+      <c r="K10" s="16">
+        <v>50</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="21"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="186"/>
+      <c r="B11" s="194"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="43">
+        <v>1800000</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="37">
+        <v>1000000</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="16">
+        <v>50</v>
+      </c>
+      <c r="L11" s="22"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="25"/>
+      <c r="W11" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="186"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="43">
+        <v>460000</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="37">
+        <v>500000</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="16">
+        <v>50</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="21"/>
+      <c r="W12" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="186"/>
+      <c r="B13" s="194"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="190">
+        <v>5100000</v>
+      </c>
+      <c r="E13" s="193" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="36">
+        <v>250000</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="165" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13">
+        <v>50</v>
+      </c>
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="25"/>
+      <c r="W13" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="186"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="192"/>
+      <c r="D14" s="191"/>
+      <c r="E14" s="195"/>
+      <c r="F14" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="37">
+        <v>25000</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="167"/>
+      <c r="K14" s="16">
+        <v>50</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="21"/>
+      <c r="W14" s="5"/>
+    </row>
+    <row r="15" spans="1:23" ht="18" customHeight="1">
+      <c r="A15" s="186"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="61">
+        <v>3600000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15">
+        <v>50</v>
+      </c>
+      <c r="L15" s="63"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="65"/>
+      <c r="W15" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="246" customHeight="1">
+      <c r="A16" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="54">
+        <v>0</v>
+      </c>
+      <c r="H16" s="57">
+        <v>2600000</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="54">
+        <v>50</v>
+      </c>
+      <c r="L16" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+    </row>
+    <row r="17" spans="1:21" ht="71.25">
+      <c r="A17" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="54">
+        <v>0</v>
+      </c>
+      <c r="H17" s="59">
+        <v>450000</v>
+      </c>
+      <c r="I17" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="54">
+        <v>50</v>
+      </c>
+      <c r="L17" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+    </row>
+    <row r="18" spans="1:21" ht="60" customHeight="1">
+      <c r="A18" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="54">
+        <v>0</v>
+      </c>
+      <c r="H18" s="66">
+        <v>900955</v>
+      </c>
+      <c r="I18" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="54">
+        <v>50</v>
+      </c>
+      <c r="L18" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+    </row>
+    <row r="19" spans="1:21" ht="57">
+      <c r="A19" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B19" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="54"/>
+      <c r="D19" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="54">
+        <v>0</v>
+      </c>
+      <c r="H19" s="67">
+        <v>630000</v>
+      </c>
+      <c r="I19" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="54">
+        <v>50</v>
+      </c>
+      <c r="L19" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+    </row>
+    <row r="20" spans="1:21" ht="28.5">
+      <c r="A20" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B20" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="54">
+        <v>0</v>
+      </c>
+      <c r="H20" s="69">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="54">
+        <v>50</v>
+      </c>
+      <c r="L20" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+    </row>
+    <row r="21" spans="1:21" ht="48.75" customHeight="1">
+      <c r="A21" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B21" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="54"/>
+      <c r="D21" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="54">
+        <v>0</v>
+      </c>
+      <c r="H21" s="66">
+        <v>95800</v>
+      </c>
+      <c r="I21" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="54">
+        <v>50</v>
+      </c>
+      <c r="L21" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+    </row>
+    <row r="22" spans="1:21" ht="42.75">
+      <c r="A22" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B22" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="54">
+        <v>0</v>
+      </c>
+      <c r="H22" s="66">
+        <v>10700</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="54">
+        <v>50</v>
+      </c>
+      <c r="L22" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+    </row>
+    <row r="23" spans="1:21" ht="56.25" customHeight="1">
+      <c r="A23" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B23" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="54"/>
+      <c r="D23" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="54">
+        <v>0</v>
+      </c>
+      <c r="H23" s="57">
+        <v>35800000</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="58"/>
+      <c r="K23" s="54">
+        <v>50</v>
+      </c>
+      <c r="L23" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+    </row>
+    <row r="24" spans="1:21" ht="85.5">
+      <c r="A24" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B24" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="54"/>
+      <c r="D24" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="54">
+        <v>0</v>
+      </c>
+      <c r="H24" s="57">
+        <v>35800000</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" s="54">
+        <v>50</v>
+      </c>
+      <c r="L24" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="54"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+    </row>
+    <row r="25" spans="1:21" ht="57">
+      <c r="A25" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B25" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="54">
+        <v>0</v>
+      </c>
+      <c r="H25" s="57">
+        <v>35800000</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="54">
+        <v>50</v>
+      </c>
+      <c r="L25" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M25" s="54"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="54"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+    </row>
+    <row r="26" spans="1:21" ht="71.25">
+      <c r="A26" s="54">
+        <v>134106</v>
+      </c>
+      <c r="B26" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="54"/>
+      <c r="D26" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="54">
+        <v>0</v>
+      </c>
+      <c r="H26" s="57">
+        <v>35800000</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="K26" s="54">
+        <v>50</v>
+      </c>
+      <c r="L26" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="54"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="J4:J6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A7:A15"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B7:B15"/>
+  </mergeCells>
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q15" xr:uid="{F258C04C-A4FA-4805-B174-3B4E93F9594B}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N15" xr:uid="{C4A7DBCA-C2D6-4FA5-982F-5A3428C7B505}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O15" xr:uid="{F127BD6B-DABA-4CD0-B7EC-5D6ADA771134}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M15" xr:uid="{0D926631-4967-407F-9CB9-1417932425E3}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T15" xr:uid="{C1C18A2E-EA97-4EAA-BEB7-A7C718449DA8}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P15" xr:uid="{03233118-9D4D-48D3-8D64-4D826D3A4A45}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L15" xr:uid="{BA657230-24E8-4FBF-8E54-DAC070803EF0}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R15" xr:uid="{C66D08F0-1978-4285-8B45-EF57F48BC972}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S15" xr:uid="{D7824502-832B-4546-85D0-CDD293CA8C7E}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{C4FD8662-769B-494E-9138-E94D4C1D1E56}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{9A26C6CC-A90B-4470-9438-1D477C2A7711}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{CCBDE4FC-898C-4115-BF85-B3ECC1B4C291}"/>
+    <hyperlink ref="C16" r:id="rId5" xr:uid="{4569EF7E-B390-4585-84F1-A2102C6933C5}"/>
+    <hyperlink ref="C17" r:id="rId6" xr:uid="{3DB16031-E6AF-4F6D-964B-F482AD975E53}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId7"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1619D449-50B6-4A9C-AD6A-E75333A47C33}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E7:E8 E11:E13 E15 E2:E4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="66.42578125" customWidth="1"/>
     <col min="3" max="3" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="76.5">
-      <c r="A2" s="77" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>52</v>
+    <row r="2" spans="1:2" ht="57">
+      <c r="A2" s="197" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30.75">
-      <c r="A3" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="60.75">
-      <c r="A4" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="60.75">
-      <c r="A5" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="183">
-      <c r="A6" s="77" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="76.5">
-      <c r="A7" s="77" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="76.5">
-      <c r="A8" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="76.5">
-      <c r="A9" s="77" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="76.5">
-      <c r="A10" s="77" t="s">
+      <c r="A3" s="197" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="78" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="60.75">
-      <c r="A11" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="78" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="76.5">
-      <c r="A12" s="77" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="45.75">
-      <c r="A13" s="77" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30.75">
-      <c r="A14" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="78" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="45.75">
-      <c r="A15" s="77" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45.75">
-      <c r="A16" s="77" t="s">
+      <c r="B3" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="57">
+      <c r="A4" s="197" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="57">
+      <c r="A5" s="197" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="156.75">
+      <c r="A6" s="197" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="71.25">
+      <c r="A7" s="197" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="71.25">
+      <c r="A8" s="197" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="71.25">
+      <c r="A9" s="197" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="57">
+      <c r="A10" s="197" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="199" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="57">
+      <c r="A11" s="197" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="199" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="71.25">
+      <c r="A12" s="197" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="78" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="60.75">
-      <c r="A17" s="77" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="60.75">
-      <c r="A18" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="78" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="152.25">
-      <c r="A19" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="78" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="45.75">
-      <c r="A20" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="76.5">
-      <c r="A21" s="77" t="s">
+      <c r="B12" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28.5">
+      <c r="A13" s="197" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="199" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="28.5">
+      <c r="A14" s="197" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="199" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="42.75">
+      <c r="A15" s="197" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="199" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="42.75">
+      <c r="A16" s="197" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="199" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="57">
+      <c r="A17" s="197" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="57">
+      <c r="A18" s="197" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="199" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="128.25">
+      <c r="A19" s="197" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="199" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="42.75">
+      <c r="A20" s="197" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="199" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="71.25">
+      <c r="A21" s="197" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="79" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="45.75">
-      <c r="A22" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="78" t="s">
-        <v>91</v>
+      <c r="B21" s="200" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="42.75">
+      <c r="A22" s="197" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="199" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2474,6 +7203,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2491,23 +7229,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBFBB887-5DC5-4CC5-B981-61FC103489AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D518B4E-C20A-4FFC-BC13-992313191C2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E1EBA35-2B5F-4AEF-A4D2-B5ABF7D7A146}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E1EBA35-2B5F-4AEF-A4D2-B5ABF7D7A146}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D518B4E-C20A-4FFC-BC13-992313191C2A}"/>
 </file>
--- a/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Ukraine - Energy Projects.xlsx
@@ -1058,13 +1058,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="43" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1176,6 +1176,7 @@
     <author>tc={DCF56ECC-FA71-46B4-8431-C6926AD78D1B}</author>
     <author>tc={936BA648-9D7A-44C5-A1B1-668994676C0D}</author>
     <author>tc={F6E347AD-C5A2-4313-AAB4-029A64DA333D}</author>
+    <author>CO validation update</author>
   </authors>
   <commentList>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -1208,6 +1209,16 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Please provide any assumption or comments on how you estimate the number of beneficiaries</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="4" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="4" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
       </text>
     </comment>
   </commentList>
@@ -1918,7 +1929,7 @@
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="J3" s="33" t="inlineStr">
+      <c r="J3" s="198" t="inlineStr">
         <is>
           <t>No. of Beneficaries</t>
         </is>
@@ -1954,20 +1965,17 @@
       <c r="Z3" s="110" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="n"/>
-      <c r="B4" s="198" t="n"/>
       <c r="C4" s="196" t="n"/>
-      <c r="D4" s="198" t="n"/>
-      <c r="E4" s="198" t="n"/>
-      <c r="F4" s="198" t="n"/>
-      <c r="G4" s="198" t="n"/>
-      <c r="H4" s="198" t="n"/>
       <c r="I4" s="65" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="J4" s="198" t="n"/>
+      <c r="J4" s="198" t="inlineStr">
+        <is>
+          <t>No. of Beneficaries</t>
+        </is>
+      </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
@@ -1979,7 +1987,6 @@
           <t>-Transporation Support for 7 Autotransformers</t>
         </is>
       </c>
-      <c r="N4" s="198" t="n"/>
       <c r="O4" t="n">
         <v>50</v>
       </c>
@@ -1995,20 +2002,17 @@
       <c r="Z4" s="110" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="207" t="n"/>
-      <c r="B5" s="33" t="n"/>
       <c r="C5" s="29" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="33" t="n"/>
-      <c r="H5" s="33" t="n"/>
       <c r="I5" s="29" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="J5" s="33" t="n"/>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>No. of Beneficaries</t>
+        </is>
+      </c>
       <c r="K5" s="16" t="n">
         <v>0</v>
       </c>
@@ -2020,7 +2024,6 @@
           <t xml:space="preserve">-1 gas turbine for power generation </t>
         </is>
       </c>
-      <c r="N5" s="33" t="n"/>
       <c r="O5" s="16" t="n">
         <v>50</v>
       </c>
@@ -2036,14 +2039,7 @@
       <c r="Z5" s="110" t="n"/>
     </row>
     <row r="6" ht="361.5" customHeight="1">
-      <c r="A6" s="207" t="n"/>
-      <c r="B6" s="33" t="n"/>
       <c r="C6" s="29" t="n"/>
-      <c r="D6" s="33" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="33" t="n"/>
-      <c r="H6" s="33" t="n"/>
       <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2054,16 +2050,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K6" s="16" t="n">
+      <c r="K6" s="207" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="208" t="n"/>
-      <c r="M6" s="209" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N6" s="33" t="n"/>
+      <c r="M6" s="41" t="n"/>
       <c r="O6" s="16" t="n"/>
       <c r="P6" s="19" t="n"/>
       <c r="Q6" s="20" t="n"/>
@@ -2095,9 +2086,9 @@
       <c r="D7" s="131" t="n">
         <v>64600000</v>
       </c>
-      <c r="E7" s="210" t="n"/>
-      <c r="F7" s="210" t="n"/>
-      <c r="G7" s="210" t="n"/>
+      <c r="E7" s="209" t="n"/>
+      <c r="F7" s="209" t="n"/>
+      <c r="G7" s="209" t="n"/>
       <c r="H7" s="131" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2707,13 +2698,12 @@
         </is>
       </c>
       <c r="C19" s="122" t="n"/>
-      <c r="D19" s="147">
-        <f>6772151.9+241257.912</f>
-        <v/>
-      </c>
-      <c r="E19" s="211" t="n"/>
-      <c r="F19" s="211" t="n"/>
-      <c r="G19" s="211" t="n"/>
+      <c r="D19" s="147" t="n">
+        <v>7013409.812000001</v>
+      </c>
+      <c r="E19" s="210" t="n"/>
+      <c r="F19" s="210" t="n"/>
+      <c r="G19" s="210" t="n"/>
       <c r="H19" s="147" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2932,13 +2922,7 @@
       <c r="H24" s="137" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="A3:A5"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -2965,12 +2949,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -3366,7 +3344,7 @@
       <c r="W5" s="110" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="207" t="n"/>
+      <c r="A6" s="211" t="n"/>
       <c r="B6" s="33" t="n"/>
       <c r="C6" s="29" t="n"/>
       <c r="D6" s="33" t="n"/>
@@ -3588,9 +3566,8 @@
       <c r="A10" s="95" t="n"/>
       <c r="B10" s="111" t="n"/>
       <c r="C10" s="95" t="n"/>
-      <c r="D10" s="112">
-        <f>11915000+5164000+16500000+11000000</f>
-        <v/>
+      <c r="D10" s="112" t="n">
+        <v>44579000</v>
       </c>
       <c r="E10" s="83" t="inlineStr">
         <is>
@@ -4114,9 +4091,8 @@
         </is>
       </c>
       <c r="C20" s="122" t="n"/>
-      <c r="D20" s="147">
-        <f>6772151.9+241257.912</f>
-        <v/>
+      <c r="D20" s="147" t="n">
+        <v>7013409.812000001</v>
       </c>
       <c r="E20" s="122" t="inlineStr">
         <is>
@@ -4166,9 +4142,8 @@
       <c r="A21" s="122" t="n"/>
       <c r="B21" s="122" t="n"/>
       <c r="C21" s="122" t="n"/>
-      <c r="D21" s="147">
-        <f>1244756.78+241257.912</f>
-        <v/>
+      <c r="D21" s="147" t="n">
+        <v>1486014.692</v>
       </c>
       <c r="E21" s="122" t="inlineStr">
         <is>
@@ -4218,9 +4193,8 @@
       <c r="A22" s="122" t="n"/>
       <c r="B22" s="122" t="n"/>
       <c r="C22" s="122" t="n"/>
-      <c r="D22" s="147">
-        <f>7543903.56+241257.912</f>
-        <v/>
+      <c r="D22" s="147" t="n">
+        <v>7785161.471999999</v>
       </c>
       <c r="E22" s="122" t="inlineStr">
         <is>
@@ -4270,9 +4244,8 @@
       <c r="A23" s="126" t="n"/>
       <c r="B23" s="54" t="n"/>
       <c r="C23" s="54" t="n"/>
-      <c r="D23" s="148">
-        <f>4571202.53+241257.912</f>
-        <v/>
+      <c r="D23" s="148" t="n">
+        <v>4812460.442</v>
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
@@ -4759,7 +4732,7 @@
       <c r="W5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="207" t="n"/>
+      <c r="A6" s="211" t="n"/>
       <c r="B6" s="33" t="n"/>
       <c r="C6" s="29" t="n"/>
       <c r="D6" s="33" t="n"/>
@@ -4954,7 +4927,7 @@
       <c r="A10" s="39" t="n"/>
       <c r="B10" s="198" t="n"/>
       <c r="C10" s="198" t="n"/>
-      <c r="D10" s="207" t="n"/>
+      <c r="D10" s="211" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="74" t="inlineStr">
         <is>
@@ -5148,7 +5121,7 @@
       <c r="A14" s="39" t="n"/>
       <c r="B14" s="198" t="n"/>
       <c r="C14" s="198" t="n"/>
-      <c r="D14" s="207" t="n"/>
+      <c r="D14" s="211" t="n"/>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="74" t="inlineStr">
         <is>
@@ -6286,7 +6259,7 @@
       <c r="W5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="207" t="n"/>
+      <c r="A6" s="211" t="n"/>
       <c r="B6" s="33" t="n"/>
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="33" t="n"/>
@@ -6477,7 +6450,7 @@
       <c r="A10" s="39" t="n"/>
       <c r="B10" s="198" t="n"/>
       <c r="C10" s="198" t="n"/>
-      <c r="D10" s="207" t="n"/>
+      <c r="D10" s="211" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="inlineStr">
         <is>
@@ -6671,7 +6644,7 @@
       <c r="A14" s="39" t="n"/>
       <c r="B14" s="198" t="n"/>
       <c r="C14" s="198" t="n"/>
-      <c r="D14" s="207" t="n"/>
+      <c r="D14" s="211" t="n"/>
       <c r="E14" s="33" t="n"/>
       <c r="F14" s="33" t="inlineStr">
         <is>
